--- a/AAII_Financials/Quarterly/ROIV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ROIV_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="92">
   <si>
     <t>ROIV</t>
   </si>
@@ -656,389 +656,402 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E8" s="3">
         <v>2500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>15600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4500</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3">
         <v>17100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>12500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>9200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>24300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>14000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>15100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1600</v>
       </c>
-      <c r="AB8" s="3">
-        <v>0</v>
-      </c>
       <c r="AC8" s="3">
         <v>0</v>
       </c>
       <c r="AD8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>202300</v>
+      </c>
+      <c r="E9" s="3">
         <v>199300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>166100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>164200</v>
       </c>
-      <c r="G9" s="3">
-        <v>152600</v>
-      </c>
       <c r="H9" s="3">
+        <v>153100</v>
+      </c>
+      <c r="I9" s="3">
         <v>145000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>140200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>141400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>118900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>106000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>100200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>115000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>110400</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>3600</v>
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R9" s="3">
         <v>3600</v>
       </c>
       <c r="S9" s="3">
+        <v>3600</v>
+      </c>
+      <c r="T9" s="3">
         <v>1700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>6400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>500</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>700</v>
       </c>
       <c r="Z9" s="3">
         <v>700</v>
       </c>
       <c r="AA9" s="3">
+        <v>700</v>
+      </c>
+      <c r="AB9" s="3">
         <v>200</v>
       </c>
-      <c r="AB9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-200900</v>
+      </c>
+      <c r="E10" s="3">
         <v>-196700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-164100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-162600</v>
       </c>
-      <c r="G10" s="3">
-        <v>-150400</v>
-      </c>
       <c r="H10" s="3">
+        <v>-150900</v>
+      </c>
+      <c r="I10" s="3">
         <v>-137500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-131100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-136900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-110900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-96900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-84700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-111400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-105900</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3">
         <v>13500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>8900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>8700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>22900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>7600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>7000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>14600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>5100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1400</v>
       </c>
-      <c r="AB10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1069,94 +1082,98 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>202000</v>
+      </c>
+      <c r="E12" s="3">
         <v>198900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>165400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>164600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>152900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>145200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>141600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>143100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>120500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>107600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>108100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>128700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>121900</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3">
         <v>125500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>132000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>135800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>136600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>153500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>254300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>78600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>474400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>202300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>97400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>58700</v>
       </c>
-      <c r="AB12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1241,94 +1258,100 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-770200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-21600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-114400</v>
       </c>
-      <c r="G14" s="3">
-        <v>25400</v>
-      </c>
       <c r="H14" s="3">
+        <v>21200</v>
+      </c>
+      <c r="I14" s="3">
         <v>-96200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>32200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-39900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-116900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-21100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-5302600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>42400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>20100</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
         <v>85200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-16800</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>-5000</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W14" s="3">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X14" s="3">
         <v>-66500</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>-28800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-86500</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
         <v>0</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1336,44 +1359,44 @@
         <v>600</v>
       </c>
       <c r="E15" s="3">
+        <v>600</v>
+      </c>
+      <c r="F15" s="3">
         <v>700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>8200</v>
-      </c>
-      <c r="I15" s="3">
-        <v>1900</v>
       </c>
       <c r="J15" s="3">
         <v>1900</v>
       </c>
       <c r="K15" s="3">
+        <v>1900</v>
+      </c>
+      <c r="L15" s="3">
         <v>2000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>13800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>5600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>5800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>6000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1413,8 +1436,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1442,180 +1468,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>367800</v>
+      </c>
+      <c r="E17" s="3">
         <v>372300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>341100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>293700</v>
       </c>
-      <c r="G17" s="3">
-        <v>280800</v>
-      </c>
       <c r="H17" s="3">
+        <v>285000</v>
+      </c>
+      <c r="I17" s="3">
         <v>372700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>272500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>337700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>211900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>205700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>201200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>203600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>201700</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3">
         <v>382600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>276500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>286600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>271000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>270400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>698400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>95700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>556000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>264800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>129000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>29500</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-366400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-369800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-339100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-292100</v>
       </c>
-      <c r="G18" s="3">
-        <v>-278600</v>
-      </c>
       <c r="H18" s="3">
+        <v>-282800</v>
+      </c>
+      <c r="I18" s="3">
         <v>-365200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-263500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-333200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-203900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-196600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-185700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-199900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-197200</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3">
         <v>-365500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-264000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-282300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-261800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-246100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-684400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-88000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-540900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-259000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-127700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-27900</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1646,148 +1679,152 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-12600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>16100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>26700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>13500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-11300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>8700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>13300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>43000</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3">
         <v>-8100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-41400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-64800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-28200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-58500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>460700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-10500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-21600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-16100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>75500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>21900</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-367900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-356600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-354500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-317900</v>
       </c>
-      <c r="G21" s="3">
-        <v>-291100</v>
-      </c>
       <c r="H21" s="3">
+        <v>-295300</v>
+      </c>
+      <c r="I21" s="3">
         <v>-345700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-262200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-332100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-206600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-191500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-178500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-207700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-234400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>6000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-368500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-298400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-346500</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1818,8 +1855,11 @@
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1862,222 +1902,231 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3">
         <v>8400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>8300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>2600</v>
-      </c>
-      <c r="T22" s="3">
-        <v>1500</v>
       </c>
       <c r="U22" s="3">
         <v>1500</v>
       </c>
       <c r="V22" s="3">
+        <v>1500</v>
+      </c>
+      <c r="W22" s="3">
         <v>1600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>2500</v>
-      </c>
-      <c r="X22" s="3">
-        <v>700</v>
       </c>
       <c r="Y22" s="3">
         <v>700</v>
       </c>
       <c r="Z22" s="3">
+        <v>700</v>
+      </c>
+      <c r="AA22" s="3">
         <v>600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>800</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
-      </c>
       <c r="AC22" s="3">
         <v>0</v>
       </c>
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-294600</v>
+      </c>
+      <c r="E23" s="3">
         <v>454100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-290400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-159000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-269300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-203100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-234500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-224400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-19600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-100700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5153500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-241400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-243600</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3">
         <v>-382100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-313800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-349800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-291500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-306000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-225200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-101000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-563200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-275800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-52800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-6800</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E24" s="3">
         <v>98400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>23300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>49300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-25600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>12500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>12000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-5800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>22400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1700</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3">
         <v>2800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>4000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-200</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>100</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
       <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>-200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1200</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2162,180 +2211,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-290600</v>
+      </c>
+      <c r="E26" s="3">
         <v>355700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-313700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-166000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-273900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-252400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-208900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-236800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-31600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-95000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5131200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-244600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-245200</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3">
         <v>-384900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-315900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-353800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-291300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-306100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-225600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-101100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-563200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-275600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-53500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-189800</v>
+      </c>
+      <c r="E27" s="3">
         <v>303000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-265900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-113500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-223400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-206500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>169400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-230200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>95300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-151100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5096200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-304300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-291800</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3">
         <v>-352000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-291600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-331800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-270100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-284500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-208500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-82200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-509600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-261000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-35400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2420,8 +2478,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2441,31 +2502,31 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>327000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-43100</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>89100</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-87500</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-58500</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-86500</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-82600</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>3</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>3</v>
@@ -2479,8 +2540,8 @@
       <c r="U29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
+      <c r="V29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W29" s="3">
         <v>0</v>
@@ -2506,8 +2567,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2592,8 +2656,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2678,180 +2745,189 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E32" s="3">
         <v>12600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-16100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-26700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-13500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>11300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-8700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-13300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-43000</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3">
         <v>8100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>41400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>64800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>28200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>58500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-460700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>10500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>21600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>16100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-75500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-21900</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-189800</v>
+      </c>
+      <c r="E33" s="3">
         <v>303000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-265900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-113500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-223400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-206500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>169400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-230200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>95300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-151100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5096200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-304300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-291800</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3">
         <v>-352000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-291600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-331800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-270100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-284500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-208500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-82200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-509600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-261000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-35400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2936,185 +3012,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-189800</v>
+      </c>
+      <c r="E35" s="3">
         <v>303000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-265900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-113500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-223400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-206500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>169400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-230200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>95300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-151100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5096200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-304300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-291800</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3">
         <v>-352000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-291600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-331800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-270100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-284500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-208500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-82200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-509600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-261000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-35400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3145,8 +3230,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3177,74 +3263,75 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1248500</v>
+      </c>
+      <c r="E41" s="3">
         <v>1419200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1478300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1237000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1238500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2715400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1990700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1958600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5678500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6495000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6670800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1408200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1434100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1676800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1527400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1599000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1942200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2060400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2214300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2497300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1996700</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3263,35 +3350,38 @@
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2593600</v>
+      </c>
+      <c r="E42" s="3">
         <v>2872600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3051700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3148800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3264700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2171500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3155800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3428000</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -3349,13 +3439,16 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>770200</v>
+        <v>21600</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>3</v>
@@ -3369,54 +3462,54 @@
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3">
         <v>143800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>22700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>215200</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3">
         <v>63200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>54600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>39900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>37600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>29500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>27400</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U43" s="3">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V43" s="3">
         <v>11500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>12300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5400</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3426,8 +3519,8 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB43" s="3">
-        <v>0</v>
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC43" s="3">
         <v>0</v>
@@ -3435,8 +3528,11 @@
       <c r="AD43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3461,27 +3557,27 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3">
         <v>34000</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N44" s="3">
         <v>5200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2800</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3494,8 +3590,8 @@
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V44" s="3">
-        <v>0</v>
+      <c r="V44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W44" s="3">
         <v>0</v>
@@ -3521,74 +3617,77 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>101500</v>
+        <v>874200</v>
       </c>
       <c r="E45" s="3">
+        <v>871700</v>
+      </c>
+      <c r="F45" s="3">
         <v>127300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>123600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>110300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>110800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>12900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>333800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>11100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>233800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>9700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>17700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>13000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>15500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>89300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>88500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>97200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>86100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>61700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>46100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>55500</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3607,74 +3706,77 @@
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4742100</v>
+      </c>
+      <c r="E46" s="3">
         <v>5167400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4659900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4511600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4615800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5000100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5364000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5801100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6001500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6731800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6806700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1551600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1561200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1798600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1646200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1714900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2039400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2146500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2287500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2555800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2057600</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3693,74 +3795,77 @@
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>444600</v>
+      </c>
+      <c r="E47" s="3">
         <v>408000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>433900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>412300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>283800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>302900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>290000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>311400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>263000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>247800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>239900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>250400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>296200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>304300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>272500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>246600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>301300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>325800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>398700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>436800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>280900</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3779,74 +3884,77 @@
       <c r="AD47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>90200</v>
+      </c>
+      <c r="E48" s="3">
         <v>92400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>97000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>110800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>101900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>101100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>104500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>56700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>63200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>59300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>68800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>73100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>87900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>92300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>91900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>92300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>91100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>86900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>83300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>80100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>80700</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3856,8 +3964,8 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB48" s="3">
-        <v>0</v>
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC48" s="3">
         <v>0</v>
@@ -3865,8 +3973,11 @@
       <c r="AD48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3892,35 +4003,35 @@
         <v>0</v>
       </c>
       <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
         <v>136000</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
       <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
         <v>150400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>140600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>145000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>144900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>146100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>140300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>145400</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3936,8 +4047,8 @@
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z49" s="3">
-        <v>0</v>
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA49" s="3">
         <v>0</v>
@@ -3951,8 +4062,11 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4037,8 +4151,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4123,74 +4240,77 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>29600</v>
+      </c>
+      <c r="E52" s="3">
         <v>40900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>34600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>27800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>31100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>32900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>33900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>36900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>32800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>183600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>46800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>49800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>46300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>49500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>46200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>21500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>23100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>25800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>29800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>30300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>35500</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4209,8 +4329,11 @@
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4295,74 +4418,77 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5306500</v>
+      </c>
+      <c r="E54" s="3">
         <v>5708700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5225400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5062600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5032600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5436900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5792300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6206000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6496400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7222500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7312700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2065500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2136600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2389600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2203000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2215500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2600400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2585100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2799400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3102900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2454700</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4381,8 +4507,11 @@
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4413,8 +4542,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4445,74 +4575,75 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>25100</v>
+      </c>
+      <c r="E57" s="3">
         <v>18000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>13300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>15100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>11600</v>
-      </c>
-      <c r="H57" s="3">
-        <v>23700</v>
       </c>
       <c r="I57" s="3">
         <v>23700</v>
       </c>
       <c r="J57" s="3">
+        <v>23700</v>
+      </c>
+      <c r="K57" s="3">
         <v>25100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>27700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>14000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>35200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>44100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>50000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>37800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>48000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>41400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>161300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>34600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>24400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>77200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>15000</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4531,62 +4662,65 @@
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E58" s="3">
         <v>11100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>10400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>9000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>9400</v>
-      </c>
-      <c r="H58" s="3">
-        <v>9800</v>
       </c>
       <c r="I58" s="3">
         <v>9800</v>
       </c>
       <c r="J58" s="3">
+        <v>9800</v>
+      </c>
+      <c r="K58" s="3">
         <v>9500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>21500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>9000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>56200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>59900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>55800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>52400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>37700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>35800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>33300</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4602,14 +4736,14 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z58" s="3">
-        <v>0</v>
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>3</v>
+      <c r="AB58" s="3">
+        <v>0</v>
       </c>
       <c r="AC58" s="3" t="s">
         <v>3</v>
@@ -4617,74 +4751,77 @@
       <c r="AD58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>77400</v>
+      </c>
+      <c r="E59" s="3">
         <v>46300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>10200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>410100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>27500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>124300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>31300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>19900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>15100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>158500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>153600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>134300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>149800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>136400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>226300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>194100</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4703,74 +4840,77 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>283600</v>
+      </c>
+      <c r="E60" s="3">
         <v>281200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>152000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>133900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>113900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>149400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>141500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>556200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>215000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>266800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>244900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>265500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>245000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>272400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>244300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>230700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>328900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>184400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>160700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>303400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>209200</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4789,74 +4929,77 @@
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>94800</v>
+      </c>
+      <c r="E61" s="3">
         <v>96300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>98500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>89800</v>
-      </c>
-      <c r="G61" s="3">
-        <v>90300</v>
       </c>
       <c r="H61" s="3">
         <v>90300</v>
       </c>
       <c r="I61" s="3">
+        <v>90300</v>
+      </c>
+      <c r="J61" s="3">
         <v>90500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>43200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>357600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>45000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>450400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>438100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>436900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>429000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>375100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>376100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>383700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>210000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>204000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>199900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>186400</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4875,74 +5018,77 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E62" s="3">
         <v>38700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>33400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>12500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>10000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>24400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>26500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>28500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>462200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>32800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>36300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>120600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>80600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>156400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>94600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>109900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>129300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>164900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>148700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>79400</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4961,8 +5107,11 @@
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5047,8 +5196,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5133,8 +5285,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5219,74 +5374,77 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>384600</v>
+      </c>
+      <c r="E66" s="3">
         <v>416300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>251100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>257100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>216700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>249700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>256400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>626000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>601200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>774000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>728100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>739900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>802500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>782000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1247400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1054900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1216300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>928200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>933700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1064900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>731600</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5305,8 +5463,11 @@
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5337,8 +5498,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5423,8 +5585,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5509,8 +5674,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5595,8 +5763,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5681,74 +5852,77 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-900400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-501800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-695000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-429100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-315600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>116100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>460400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>395600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>671500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>576200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>727300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-4368900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-4064600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-3772800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-3739100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-3387100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-3095500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-2763700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-2493700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-2209100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-2000600</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5767,8 +5941,11 @@
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5853,8 +6030,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5939,8 +6119,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6025,74 +6208,77 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4231300</v>
+      </c>
+      <c r="E76" s="3">
         <v>4527400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4269300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4362300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4345600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4687600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5189500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5153000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5435300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5968600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6089800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>948500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>910700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1157800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>955500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1160600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1384100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1656900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1865700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2038000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1723100</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6111,8 +6297,11 @@
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6197,185 +6386,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-189800</v>
+      </c>
+      <c r="E81" s="3">
         <v>303000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-265900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-113500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-223400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-206500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>169400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-230200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>95300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-151100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5096200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-304300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-291800</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3">
         <v>-352000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-291600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-331800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-270100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-284500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-208500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-82200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-509600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-261000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-35400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6406,56 +6604,57 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E83" s="3">
         <v>8200</v>
-      </c>
-      <c r="E83" s="3">
-        <v>1900</v>
       </c>
       <c r="F83" s="3">
         <v>1900</v>
       </c>
       <c r="G83" s="3">
+        <v>1900</v>
+      </c>
+      <c r="H83" s="3">
         <v>2000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>13800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2500</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3">
         <v>3500</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3">
         <v>2900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5200</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6471,8 +6670,8 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X83" s="3">
-        <v>0</v>
+      <c r="X83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y83" s="3">
         <v>0</v>
@@ -6492,8 +6691,11 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6578,8 +6780,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6664,8 +6869,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6750,8 +6958,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6836,8 +7047,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6922,94 +7136,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-270500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-163800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-196500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-185700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-204400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-172600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-207300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-266800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-192800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-108500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-210500</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3">
         <v>-249900</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3">
         <v>-222600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-189600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-252100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-147500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-268500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-120600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-141200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-106100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-236900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-98000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-111200</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7040,94 +7260,98 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>4900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1800</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-1000</v>
       </c>
       <c r="K91" s="3">
         <v>-1000</v>
       </c>
       <c r="L91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-400</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O91" s="3">
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3">
         <v>-400</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q91" s="3">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3">
         <v>-500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-7500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-6300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-6100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-300</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
-      </c>
       <c r="AC91" s="3">
         <v>0</v>
       </c>
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7212,8 +7436,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7298,94 +7525,100 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>281300</v>
+      </c>
+      <c r="E94" s="3">
         <v>173500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>109500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>120400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1085700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>1074200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>454100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3293600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>6900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>5233000</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3">
         <v>100</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3">
         <v>-3500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-146900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-7500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-5700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-6100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>317400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-25600</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
       <c r="AC94" s="3">
         <v>0</v>
       </c>
       <c r="AD94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7416,8 +7649,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7460,8 +7694,8 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -7502,8 +7736,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7588,8 +7825,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7674,8 +7914,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7760,124 +8003,130 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-181500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-68800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>328200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>62600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-187800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-177200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-273000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-109100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-660600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-32600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>236600</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3">
         <v>7500</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3">
         <v>154500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-7300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>142000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-8400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>303900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>10200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>98700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>176000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>181100</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>5000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>3000</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
@@ -7905,8 +8154,8 @@
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
+      <c r="V101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W101" s="3">
         <v>0</v>
@@ -7932,90 +8181,96 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-170400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-57800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>241600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1477100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>724000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-27200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3664400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-857200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-135000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>5262300</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>-242500</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
       <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>-71600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-343800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-117600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-152100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-283000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>500700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-133300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-11400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-236500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>76000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>44300</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
